--- a/etf_holdings/2026-10-13_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-10-13_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,7 +469,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00985A(69,000)、00992A(23,000)、00405A(80,000)</t>
+          <t>00985A(69,000)、00405A(80,000)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -481,12 +481,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -499,24 +499,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00985A(15,000)、00992A(6,000)</t>
+          <t>00403A(43,000)、00400A(12,000)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00993A(-8,000)</t>
+          <t>00985A(-19,000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -529,88 +529,88 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>00403A(43,000)、00400A(12,000)</t>
+          <t>00993A(4,000)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>00985A(-19,000)</t>
+          <t>00981A(-193,000)、00403A(-180,000)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>00985A(23,000)、00992A(1,000)、00993A(5,000)</t>
+          <t>00993A(60,000)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00405A(-695,000)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>00985A(27,000)、00992A(1,000)</t>
+          <t>00985A(3,038,000)、00993A(19,000)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>00993A(-2,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -619,28 +619,28 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>00992A(5,000)、00993A(8,000)</t>
+          <t>00985A(15,000)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>00985A(-250,000)</t>
+          <t>00993A(-8,000)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -649,54 +649,54 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>00993A(4,000)</t>
+          <t>00985A(429,000)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>00981A(-193,000)、00403A(-180,000)</t>
+          <t>00993A(-12,000)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>00992A(18,000)、00993A(1,000)</t>
+          <t>00403A(新納入)、00993A(1,000)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>00985A(-43,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -704,29 +704,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>00993A(60,000)</t>
+          <t>00985A(90,000)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>00405A(-695,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -734,29 +734,29 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>00985A(3,038,000)、00993A(19,000)</t>
+          <t>00993A(7,000)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00985A(-40,000)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -764,29 +764,29 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>00992A(16,000)、00993A(8,000)</t>
+          <t>00985A(124,000)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00993A(-30,000)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -794,29 +794,29 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>00985A(429,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>00993A(-12,000)</t>
+          <t>00981A(-4,313,000)、00990A(-698,000)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -829,7 +829,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>00403A(新納入)、00993A(1,000)</t>
+          <t>00985A(23,000)、00993A(5,000)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -841,12 +841,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -859,7 +859,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>00985A(90,000)、00400A(新納入)</t>
+          <t>00985A(178,000)、00993A(13,000)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -871,12 +871,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>昇達科</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -884,29 +884,29 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>00992A(2,000)、00993A(1,000)</t>
+          <t>00993A(4,000)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00985A(-43,000)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -914,29 +914,29 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>00985A(80,000)、00992A(新納入)</t>
+          <t>00985A(27,000)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00993A(-2,000)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -944,29 +944,29 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>00985A(15,000)、00992A(10,000)</t>
+          <t>00993A(8,000)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00985A(-250,000)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -984,19 +984,19 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>00985A(-40,000)</t>
+          <t>00985A(-36,000)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1004,29 +1004,29 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>00992A(3,000)、00993A(3,000)</t>
+          <t>00981A(5,000)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00993A(-3,000)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1039,282 +1039,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>00985A(124,000)</t>
+          <t>00993A(1,000)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>00993A(-30,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>2</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>00981A(-4,313,000)、00990A(-698,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>2</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>00992A(23,000)</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>00985A(-17,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>3105</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>穩懋</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>2</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>00985A(178,000)、00993A(13,000)</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>景碩</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>00992A(16,000)、00993A(18,000)</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>00992A(30,000)</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>00400A(-40,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>3491</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>昇達科</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>2</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>00993A(4,000)</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
           <t>00985A(-43,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>2</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>00993A(7,000)</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>00985A(-36,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>2</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>00981A(5,000)</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>00993A(-3,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>台燿</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>2</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>00981A(304,000)、00992A(20,000)</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-10-13_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-10-13_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,7 +469,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00985A(69,000)、00405A(80,000)</t>
+          <t>00985A(69,000)、00992A(23,000)、00405A(80,000)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -481,12 +481,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -499,24 +499,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00403A(43,000)、00400A(12,000)</t>
+          <t>00985A(15,000)、00992A(6,000)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00985A(-19,000)</t>
+          <t>00993A(-8,000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -529,88 +529,88 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>00993A(4,000)</t>
+          <t>00403A(43,000)、00400A(12,000)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>00981A(-193,000)、00403A(-180,000)</t>
+          <t>00985A(-19,000)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>00993A(60,000)</t>
+          <t>00985A(23,000)、00992A(1,000)、00993A(5,000)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>00405A(-695,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>00985A(3,038,000)、00993A(19,000)</t>
+          <t>00985A(27,000)、00992A(1,000)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00993A(-2,000)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -619,28 +619,28 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>00985A(15,000)</t>
+          <t>00992A(5,000)、00993A(8,000)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>00993A(-8,000)</t>
+          <t>00985A(-250,000)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -649,54 +649,54 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>00985A(429,000)</t>
+          <t>00993A(4,000)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>00993A(-12,000)</t>
+          <t>00981A(-193,000)、00403A(-180,000)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>00403A(新納入)、00993A(1,000)</t>
+          <t>00992A(18,000)、00993A(1,000)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00985A(-43,000)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -704,29 +704,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>00985A(90,000)、00400A(新納入)</t>
+          <t>00993A(60,000)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00405A(-695,000)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -734,29 +734,29 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>00993A(7,000)</t>
+          <t>00985A(3,038,000)、00993A(19,000)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>00985A(-40,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -764,29 +764,29 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>00985A(124,000)</t>
+          <t>00992A(16,000)、00993A(8,000)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>00993A(-30,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -794,29 +794,29 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00985A(429,000)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>00981A(-4,313,000)、00990A(-698,000)</t>
+          <t>00993A(-12,000)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -829,7 +829,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>00985A(23,000)、00993A(5,000)</t>
+          <t>00403A(新納入)、00993A(1,000)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -841,12 +841,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -859,7 +859,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>00985A(178,000)、00993A(13,000)</t>
+          <t>00985A(90,000)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -871,12 +871,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -884,29 +884,29 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>00993A(4,000)</t>
+          <t>00992A(2,000)、00993A(1,000)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>00985A(-43,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -914,29 +914,29 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>00985A(27,000)</t>
+          <t>00985A(80,000)、00992A(新納入)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>00993A(-2,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -944,29 +944,29 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>00993A(8,000)</t>
+          <t>00985A(15,000)、00992A(10,000)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>00985A(-250,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -984,19 +984,19 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>00985A(-36,000)</t>
+          <t>00985A(-40,000)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1004,29 +1004,29 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>00981A(5,000)</t>
+          <t>00992A(3,000)、00993A(3,000)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>00993A(-3,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1039,12 +1039,282 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>00993A(1,000)</t>
+          <t>00985A(124,000)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>00993A(-30,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>00981A(-4,313,000)、00990A(-698,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>00992A(23,000)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>00985A(-17,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>00985A(178,000)、00993A(13,000)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>00992A(16,000)、00993A(18,000)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>00992A(30,000)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>00400A(-40,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>00993A(4,000)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>00985A(-43,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>00993A(7,000)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>00985A(-36,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>00981A(5,000)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>00993A(-3,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>00981A(304,000)、00992A(20,000)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
